--- a/Config/Excel/GameConfig/EmitterUpgradeConfig.xlsx
+++ b/Config/Excel/GameConfig/EmitterUpgradeConfig.xlsx
@@ -2,39 +2,368 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="12720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EmitterUpgradeConfig" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="20">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -42,15 +371,305 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -403,7 +1022,6 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -413,8 +1031,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:K35"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <cols>
+    <col width="16.0288461538462" customWidth="1" min="2" max="2"/>
+    <col width="17.3076923076923" customWidth="1" min="3" max="3"/>
+    <col width="16.0288461538462" customWidth="1" min="4" max="4"/>
+    <col width="14.7403846153846" customWidth="1" min="5" max="5"/>
+    <col width="20.1923076923077" customWidth="1" min="6" max="6"/>
+    <col width="26.2788461538462" customWidth="1" min="7" max="7"/>
+    <col width="23.7115384615385" customWidth="1" min="8" max="8"/>
+    <col width="17.9423076923077" customWidth="1" min="10" max="10"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -449,20 +1077,25 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>CooldownReduceMs</t>
+          <t>CooldownMs</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>RangeAdd</t>
+          <t>Range</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>WhiteDamageMultiplier</t>
+          <t>BaseDamage</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
+        <is>
+          <t>AttackRatio</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
         <is>
           <t>Desc</t>
         </is>
@@ -516,6 +1149,11 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
@@ -553,20 +1191,25 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>累计减少冷却毫秒</t>
+          <t>最终冷却毫秒</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>累计增加射程</t>
+          <t>最终攻击射程</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>白值伤害倍率</t>
+          <t>最终基础伤害</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
+        <is>
+          <t>最终攻击力系数</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>描述</t>
         </is>
@@ -574,211 +1217,1217 @@
     </row>
     <row r="4">
       <c r="B4" t="n">
-        <v>1200001</v>
+        <v>1100101</v>
       </c>
       <c r="C4" t="n">
-        <v>12000</v>
+        <v>11001</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no_upgrade_lv1</t>
+          <t>emitter_11001_lv1</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>无升级 Lv.1</t>
+          <t>迅捷发射器 Lv.1</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>550</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="I4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>无升级</t>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>迅捷发射器 Lv.1：CD 550ms，射程 6.45，基础伤害 5，攻击系数 1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="n">
-        <v>1200101</v>
+        <v>1100102</v>
       </c>
       <c r="C5" t="n">
-        <v>12001</v>
+        <v>11001</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>player_default_lv1</t>
+          <t>emitter_11001_lv2</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>玩家默认升级 Lv.1</t>
+          <t>迅捷发射器 Lv.2</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>玩家默认升级 Lv.1：CD-0ms，射程+0.00，白值倍率x1.00</t>
+        <v>6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>迅捷发射器 Lv.2：CD 500ms，射程 6.50，基础伤害 6，攻击系数 1.1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="n">
-        <v>1200102</v>
+        <v>1100103</v>
       </c>
       <c r="C6" t="n">
-        <v>12001</v>
+        <v>11001</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>player_default_lv2</t>
+          <t>emitter_11001_lv3</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>玩家默认升级 Lv.2</t>
+          <t>迅捷发射器 Lv.3</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>50</v>
+        <v>450</v>
       </c>
       <c r="H6" t="n">
-        <v>0.05</v>
+        <v>6.55</v>
       </c>
       <c r="I6" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>玩家默认升级 Lv.2：CD-50ms，射程+0.05，白值倍率x1.15</t>
+        <v>7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>迅捷发射器 Lv.3：CD 450ms，射程 6.55，基础伤害 7，攻击系数 1.2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="n">
-        <v>1200103</v>
+        <v>1100104</v>
       </c>
       <c r="C7" t="n">
-        <v>12001</v>
+        <v>11001</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>player_default_lv3</t>
+          <t>emitter_11001_lv4</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>玩家默认升级 Lv.3</t>
+          <t>迅捷发射器 Lv.4</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1</v>
+        <v>6.6</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>玩家默认升级 Lv.3：CD-100ms，射程+0.10，白值倍率x1.30</t>
+        <v>8</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>迅捷发射器 Lv.4：CD 400ms，射程 6.60，基础伤害 8，攻击系数 1.35</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="n">
-        <v>1200104</v>
+        <v>1100105</v>
       </c>
       <c r="C8" t="n">
-        <v>12001</v>
+        <v>11001</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>player_default_lv4</t>
+          <t>emitter_11001_lv5</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>玩家默认升级 Lv.4</t>
+          <t>迅捷发射器 Lv.5</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="H8" t="n">
-        <v>0.15</v>
+        <v>6.65</v>
       </c>
       <c r="I8" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>玩家默认升级 Lv.4：CD-150ms，射程+0.15，白值倍率x1.45</t>
+        <v>10</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>迅捷发射器 Lv.5：CD 350ms，射程 6.65，基础伤害 10，攻击系数 1.5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>1200105</v>
+        <v>2100101</v>
       </c>
       <c r="C9" t="n">
-        <v>12001</v>
+        <v>21001</v>
       </c>
       <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>emitter_21001_lv1</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>普通怪物发射器 Lv.1</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1650</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>普通怪物发射器 Lv.1：CD 1650ms，射程 1.15，基础伤害 4，攻击系数 0.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>2100201</v>
+      </c>
+      <c r="C10" t="n">
+        <v>21002</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>emitter_21002_lv1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>精英怪物发射器 Lv.1</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1450</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>精英怪物发射器 Lv.1：CD 1450ms，射程 1.20，基础伤害 4，攻击系数 0.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>2100301</v>
+      </c>
+      <c r="C11" t="n">
+        <v>21003</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>emitter_21003_lv1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Boss重型发射器 Lv.1</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1900</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I11" t="n">
+        <v>8</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Boss重型发射器 Lv.1：CD 1900ms，射程 1.30，基础伤害 8，攻击系数 1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>1100201</v>
+      </c>
+      <c r="C12" t="n">
+        <v>11002</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>emitter_11002_lv1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>稳态发射器 Lv.1</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H12" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="I12" t="n">
         <v>5</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>player_default_lv5</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>玩家默认升级 Lv.5</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>200</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>玩家默认升级 Lv.5：CD-200ms，射程+0.20，白值倍率x1.60</t>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>稳态发射器 Lv.1：CD 2000ms，射程 6.45，基础伤害 5，攻击系数 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>1100202</v>
+      </c>
+      <c r="C13" t="n">
+        <v>11002</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>emitter_11002_lv2</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>稳态发射器 Lv.2</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>1950</v>
+      </c>
+      <c r="H13" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I13" t="n">
+        <v>6</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>稳态发射器 Lv.2：CD 1950ms，射程 6.50，基础伤害 6，攻击系数 1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>1100203</v>
+      </c>
+      <c r="C14" t="n">
+        <v>11002</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>emitter_11002_lv3</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>稳态发射器 Lv.3</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>1900</v>
+      </c>
+      <c r="H14" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="I14" t="n">
+        <v>7</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>稳态发射器 Lv.3：CD 1900ms，射程 6.55，基础伤害 7，攻击系数 1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>1100204</v>
+      </c>
+      <c r="C15" t="n">
+        <v>11002</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>emitter_11002_lv4</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>稳态发射器 Lv.4</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>1850</v>
+      </c>
+      <c r="H15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I15" t="n">
+        <v>8</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>稳态发射器 Lv.4：CD 1850ms，射程 6.60，基础伤害 8，攻击系数 1.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>1100205</v>
+      </c>
+      <c r="C16" t="n">
+        <v>11002</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>emitter_11002_lv5</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>稳态发射器 Lv.5</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H16" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="I16" t="n">
+        <v>10</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>稳态发射器 Lv.5：CD 1800ms，射程 6.65，基础伤害 10，攻击系数 1.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>1100301</v>
+      </c>
+      <c r="C17" t="n">
+        <v>11003</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>emitter_11003_lv1</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>蓄能发射器 Lv.1</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H17" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="I17" t="n">
+        <v>5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>蓄能发射器 Lv.1：CD 3000ms，射程 6.45，基础伤害 5，攻击系数 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>1100302</v>
+      </c>
+      <c r="C18" t="n">
+        <v>11003</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>emitter_11003_lv2</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>蓄能发射器 Lv.2</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>2950</v>
+      </c>
+      <c r="H18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I18" t="n">
+        <v>6</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>蓄能发射器 Lv.2：CD 2950ms，射程 6.50，基础伤害 6，攻击系数 1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>1100303</v>
+      </c>
+      <c r="C19" t="n">
+        <v>11003</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>emitter_11003_lv3</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>蓄能发射器 Lv.3</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>2900</v>
+      </c>
+      <c r="H19" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="I19" t="n">
+        <v>7</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>蓄能发射器 Lv.3：CD 2900ms，射程 6.55，基础伤害 7，攻击系数 1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>1100304</v>
+      </c>
+      <c r="C20" t="n">
+        <v>11003</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>emitter_11003_lv4</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>蓄能发射器 Lv.4</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>2850</v>
+      </c>
+      <c r="H20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I20" t="n">
+        <v>8</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>蓄能发射器 Lv.4：CD 2850ms，射程 6.60，基础伤害 8，攻击系数 1.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>1100305</v>
+      </c>
+      <c r="C21" t="n">
+        <v>11003</v>
+      </c>
+      <c r="D21" t="n">
+        <v>5</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>emitter_11003_lv5</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>蓄能发射器 Lv.5</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>2800</v>
+      </c>
+      <c r="H21" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="I21" t="n">
+        <v>10</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>蓄能发射器 Lv.5：CD 2800ms，射程 6.65，基础伤害 10，攻击系数 1.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>1100401</v>
+      </c>
+      <c r="C22" t="n">
+        <v>11004</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>emitter_11004_lv1</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>脉冲发射器 Lv.1</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H22" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="I22" t="n">
+        <v>5</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>脉冲发射器 Lv.1：CD 4000ms，射程 6.45，基础伤害 5，攻击系数 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>1100402</v>
+      </c>
+      <c r="C23" t="n">
+        <v>11004</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>emitter_11004_lv2</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>脉冲发射器 Lv.2</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>3950</v>
+      </c>
+      <c r="H23" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I23" t="n">
+        <v>6</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>脉冲发射器 Lv.2：CD 3950ms，射程 6.50，基础伤害 6，攻击系数 1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>1100403</v>
+      </c>
+      <c r="C24" t="n">
+        <v>11004</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>emitter_11004_lv3</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>脉冲发射器 Lv.3</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>3900</v>
+      </c>
+      <c r="H24" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="I24" t="n">
+        <v>7</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>脉冲发射器 Lv.3：CD 3900ms，射程 6.55，基础伤害 7，攻击系数 1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>1100404</v>
+      </c>
+      <c r="C25" t="n">
+        <v>11004</v>
+      </c>
+      <c r="D25" t="n">
+        <v>4</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>emitter_11004_lv4</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>脉冲发射器 Lv.4</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>3850</v>
+      </c>
+      <c r="H25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I25" t="n">
+        <v>8</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>脉冲发射器 Lv.4：CD 3850ms，射程 6.60，基础伤害 8，攻击系数 1.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>1100405</v>
+      </c>
+      <c r="C26" t="n">
+        <v>11004</v>
+      </c>
+      <c r="D26" t="n">
+        <v>5</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>emitter_11004_lv5</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>脉冲发射器 Lv.5</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>3800</v>
+      </c>
+      <c r="H26" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="I26" t="n">
+        <v>10</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>脉冲发射器 Lv.5：CD 3800ms，射程 6.65，基础伤害 10，攻击系数 1.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>1100501</v>
+      </c>
+      <c r="C27" t="n">
+        <v>11005</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>emitter_11005_lv1</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>聚焦发射器 Lv.1</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H27" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="I27" t="n">
+        <v>5</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>聚焦发射器 Lv.1：CD 5000ms，射程 6.45，基础伤害 5，攻击系数 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>1100502</v>
+      </c>
+      <c r="C28" t="n">
+        <v>11005</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>emitter_11005_lv2</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>聚焦发射器 Lv.2</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>4950</v>
+      </c>
+      <c r="H28" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I28" t="n">
+        <v>6</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>聚焦发射器 Lv.2：CD 4950ms，射程 6.50，基础伤害 6，攻击系数 1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>1100503</v>
+      </c>
+      <c r="C29" t="n">
+        <v>11005</v>
+      </c>
+      <c r="D29" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>emitter_11005_lv3</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>聚焦发射器 Lv.3</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>4900</v>
+      </c>
+      <c r="H29" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="I29" t="n">
+        <v>7</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>聚焦发射器 Lv.3：CD 4900ms，射程 6.55，基础伤害 7，攻击系数 1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>1100504</v>
+      </c>
+      <c r="C30" t="n">
+        <v>11005</v>
+      </c>
+      <c r="D30" t="n">
+        <v>4</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>emitter_11005_lv4</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>聚焦发射器 Lv.4</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>4850</v>
+      </c>
+      <c r="H30" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I30" t="n">
+        <v>8</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>聚焦发射器 Lv.4：CD 4850ms，射程 6.60，基础伤害 8，攻击系数 1.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>1100505</v>
+      </c>
+      <c r="C31" t="n">
+        <v>11005</v>
+      </c>
+      <c r="D31" t="n">
+        <v>5</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>emitter_11005_lv5</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>聚焦发射器 Lv.5</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>4800</v>
+      </c>
+      <c r="H31" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="I31" t="n">
+        <v>10</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>聚焦发射器 Lv.5：CD 4800ms，射程 6.65，基础伤害 10，攻击系数 1.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>2100401</v>
+      </c>
+      <c r="C32" t="n">
+        <v>21004</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>emitter_21004_lv1</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>怪物压制发射器 Lv.1</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="I32" t="n">
+        <v>4</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>怪物压制发射器 Lv.1：CD 3000ms，射程 1.15，基础伤害 4，攻击系数 0.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>2100501</v>
+      </c>
+      <c r="C33" t="n">
+        <v>21005</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>emitter_21005_lv1</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>怪物控制发射器 Lv.1</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="I33" t="n">
+        <v>4</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>怪物控制发射器 Lv.1：CD 4000ms，射程 1.15，基础伤害 4，攻击系数 0.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>2100601</v>
+      </c>
+      <c r="C34" t="n">
+        <v>21006</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>emitter_21006_lv1</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Boss压制发射器 Lv.1</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I34" t="n">
+        <v>8</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Boss压制发射器 Lv.1：CD 3000ms，射程 1.30，基础伤害 8，攻击系数 1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>2100701</v>
+      </c>
+      <c r="C35" t="n">
+        <v>21007</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>emitter_21007_lv1</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Boss爆发发射器 Lv.1</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I35" t="n">
+        <v>8</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Boss爆发发射器 Lv.1：CD 5000ms，射程 1.30，基础伤害 8，攻击系数 1.2</t>
         </is>
       </c>
     </row>
